--- a/artfynd/A 30664-2025 artfynd.xlsx
+++ b/artfynd/A 30664-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>124825230</v>
       </c>
       <c r="B2" t="n">
-        <v>92516</v>
+        <v>92518</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 30664-2025 artfynd.xlsx
+++ b/artfynd/A 30664-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>124825230</v>
       </c>
       <c r="B2" t="n">
-        <v>92518</v>
+        <v>92520</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 30664-2025 artfynd.xlsx
+++ b/artfynd/A 30664-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>124825230</v>
       </c>
       <c r="B2" t="n">
-        <v>92520</v>
+        <v>92522</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 30664-2025 artfynd.xlsx
+++ b/artfynd/A 30664-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>124825230</v>
       </c>
       <c r="B2" t="n">
-        <v>92522</v>
+        <v>92526</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 30664-2025 artfynd.xlsx
+++ b/artfynd/A 30664-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>124825230</v>
       </c>
       <c r="B2" t="n">
-        <v>92526</v>
+        <v>92529</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
